--- a/Result/profitability/2401.xlsx
+++ b/Result/profitability/2401.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.13</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.02624999999999994</v>
+        <v>0.01750000000000006</v>
       </c>
       <c r="N2" t="n">
-        <v>44.86625</v>
+        <v>44.70125</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -681,7 +681,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0.01</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.02749999999999993</v>
+        <v>0.01500000000000006</v>
       </c>
       <c r="N3" t="n">
-        <v>41.875</v>
+        <v>41.93875</v>
       </c>
       <c r="O3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.3</v>
       </c>
       <c r="M4" t="n">
-        <v>0.006250000000000065</v>
+        <v>0.06000000000000006</v>
       </c>
       <c r="N4" t="n">
-        <v>39.61375</v>
+        <v>39.475</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -911,7 +911,7 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.42</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.03874999999999994</v>
+        <v>0.01500000000000006</v>
       </c>
       <c r="N5" t="n">
-        <v>38.39875</v>
+        <v>38.59625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.82</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1337499999999999</v>
+        <v>-0.06999999999999992</v>
       </c>
       <c r="N6" t="n">
-        <v>35.61375</v>
+        <v>35.82875</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.12</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1012499999999999</v>
+        <v>-0.04124999999999994</v>
       </c>
       <c r="N7" t="n">
-        <v>33.97375</v>
+        <v>34.2175</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.59</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.01374999999999994</v>
+        <v>0.03500000000000006</v>
       </c>
       <c r="N8" t="n">
-        <v>31.9625</v>
+        <v>31.69625</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1902,7 +1902,7 @@
         <v>0.1887500000000001</v>
       </c>
       <c r="N12" t="n">
-        <v>34.36875</v>
+        <v>34.36875000000001</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
@@ -9842,6 +9842,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2401</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2143</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1123</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1020</v>
+      </c>
+      <c r="F75" t="n">
+        <v>47.61</v>
+      </c>
+      <c r="G75" t="n">
+        <v>245</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>11.45%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>164</v>
+      </c>
+      <c r="J75" t="n">
+        <v>409</v>
+      </c>
+      <c r="K75" t="n">
+        <v>219</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.003750000000000059</v>
+      </c>
+      <c r="N75" t="n">
+        <v>47.46</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-19.5</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-2.130000000000003</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.04282267792521111</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-7.166666666666667</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>1.579999999999998</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.03432543993047998</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
